--- a/artfynd/A 21921-2025 artfynd.xlsx
+++ b/artfynd/A 21921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132511512</v>
       </c>
       <c r="B2" t="n">
-        <v>96438</v>
+        <v>96446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21921-2025 artfynd.xlsx
+++ b/artfynd/A 21921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132511512</v>
       </c>
       <c r="B2" t="n">
-        <v>96446</v>
+        <v>96456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21921-2025 artfynd.xlsx
+++ b/artfynd/A 21921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132511512</v>
       </c>
       <c r="B2" t="n">
-        <v>96456</v>
+        <v>96457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21921-2025 artfynd.xlsx
+++ b/artfynd/A 21921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132511512</v>
       </c>
       <c r="B2" t="n">
-        <v>96457</v>
+        <v>96458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21921-2025 artfynd.xlsx
+++ b/artfynd/A 21921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132511512</v>
       </c>
       <c r="B2" t="n">
-        <v>96458</v>
+        <v>96459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21921-2025 artfynd.xlsx
+++ b/artfynd/A 21921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132511512</v>
       </c>
       <c r="B2" t="n">
-        <v>96459</v>
+        <v>96461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21921-2025 artfynd.xlsx
+++ b/artfynd/A 21921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132511512</v>
       </c>
       <c r="B2" t="n">
-        <v>96461</v>
+        <v>96462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21921-2025 artfynd.xlsx
+++ b/artfynd/A 21921-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132511512</v>
+        <v>132511516</v>
       </c>
       <c r="B2" t="n">
-        <v>96468</v>
+        <v>96410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607230</v>
+        <v>607231</v>
       </c>
       <c r="R2" t="n">
-        <v>6873848</v>
+        <v>6873839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,11 +762,6 @@
           <t>barrblandskog</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>murken björklåga</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -779,6 +774,210 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132511512</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96533</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>intill Bergsjö elljusspår, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>607230</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6873848</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>murken björklåga</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131602438</v>
+      </c>
+      <c r="B4" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Masbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>607148</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6873734</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
